--- a/data/config/luban/config/general/month.xlsx
+++ b/data/config/luban/config/general/month.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -68,6 +68,9 @@
     <t>春正月</t>
   </si>
   <si>
+    <t>10001001;2000|10001002;1000</t>
+  </si>
+  <si>
     <t>春二月</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
     <t>夏四月</t>
   </si>
   <si>
+    <t>10001001;-1000|10001002;-500|10001004;-1000</t>
+  </si>
+  <si>
     <t>夏五月</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
     <t>秋七月</t>
   </si>
   <si>
+    <t>10001001;3000|10001002;1500</t>
+  </si>
+  <si>
     <t>秋八月</t>
   </si>
   <si>
@@ -93,6 +102,9 @@
   </si>
   <si>
     <t>冬十月</t>
+  </si>
+  <si>
+    <t>10001001;-5000|10001002;-2000|10001003;-1000</t>
   </si>
   <si>
     <t>冬十一月</t>
@@ -1292,7 +1304,7 @@
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="29.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="35" style="2" customWidth="1"/>
+    <col min="4" max="4" width="49.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="37.25" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.125" style="2" customWidth="1"/>
     <col min="7" max="8" width="25.375" style="2" customWidth="1"/>
@@ -1347,12 +1359,18 @@
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1361,7 +1379,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1369,7 +1390,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1377,7 +1401,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1385,6 +1412,9 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1393,7 +1423,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1401,7 +1434,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1409,7 +1445,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1417,7 +1456,10 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1425,7 +1467,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1433,7 +1478,10 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
